--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_64_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_64_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.632300000000001</v>
+        <v>6.9733</v>
       </c>
       <c r="E2" t="n">
-        <v>4.933</v>
+        <v>3.9461</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6993</v>
+        <v>3.0272</v>
       </c>
       <c r="G2" t="n">
         <v>2.4549</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1568</v>
+        <v>1.4978</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5454</v>
+        <v>0.5586</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6114</v>
+        <v>0.9392</v>
       </c>
       <c r="V2" t="n">
         <v>1.8608</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7052</v>
+        <v>4.2003</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3189</v>
+        <v>3.5115</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3864</v>
+        <v>0.6888</v>
       </c>
       <c r="G3" t="n">
         <v>2.0135</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.5632</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0474</v>
+        <v>0.2401</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0207</v>
+        <v>0.3231</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4336</v>
+        <v>3.4566</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0613</v>
+        <v>4.5213</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6277</v>
+        <v>-1.0646</v>
       </c>
       <c r="G4" t="n">
         <v>1.4574</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5302</v>
+        <v>0.5533</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3927</v>
+        <v>0.0672</v>
       </c>
       <c r="U4" t="n">
-        <v>0.923</v>
+        <v>0.4861</v>
       </c>
       <c r="V4" t="n">
         <v>1.214</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1062</v>
+        <v>2.5508</v>
       </c>
       <c r="E5" t="n">
-        <v>1.597</v>
+        <v>0.4429</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5092</v>
+        <v>2.1079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4472</v>
+        <v>0.7611</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6938</v>
+        <v>1.437</v>
       </c>
       <c r="I5" t="n">
-        <v>1.141</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4724</v>
+        <v>0.368</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6183</v>
+        <v>1.5124</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0907</v>
+        <v>-1.1445</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0252</v>
+        <v>0.3931</v>
       </c>
       <c r="N5" t="n">
         <v>-0.0755</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0502</v>
+        <v>0.4685</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4813</v>
+        <v>0.1661</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1246</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3567</v>
+        <v>0.0912</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.778</v>
+        <v>2.0357</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2963</v>
+        <v>0.7281</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0743</v>
+        <v>1.3076</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7611</v>
+        <v>0.4472</v>
       </c>
       <c r="H6" t="n">
-        <v>1.437</v>
+        <v>-0.6938</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.141</v>
       </c>
       <c r="J6" t="n">
-        <v>0.368</v>
+        <v>0.4724</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5124</v>
+        <v>-0.6183</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1445</v>
+        <v>1.0907</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3931</v>
+        <v>-0.0252</v>
       </c>
       <c r="N6" t="n">
         <v>-0.0755</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4685</v>
+        <v>0.0502</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6067</v>
+        <v>0.4107</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6642</v>
+        <v>0.2557</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0576</v>
+        <v>0.1551</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9591</v>
+        <v>1.6139</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1753</v>
+        <v>1.0957</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.5183</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7629</v>
+        <v>0.6655</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9279</v>
+        <v>-0.0539</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.165</v>
+        <v>0.7194</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9246</v>
+        <v>1.4807</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1929</v>
+        <v>0.39</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2683</v>
+        <v>1.0907</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1617</v>
+        <v>-0.8152</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2651</v>
+        <v>-0.4439</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8966</v>
+        <v>-0.3713</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0365</v>
+        <v>-0.4433</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>-0.3851</v>
       </c>
       <c r="U7" t="n">
-        <v>0.626</v>
+        <v>-0.0582</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6738</v>
+        <v>1.3973</v>
       </c>
       <c r="E8" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7502</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7629</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.9279</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-2.165</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.9246</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.1929</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.2683</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.1617</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.2651</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.8966</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4747</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.1177</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.5924</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.0814</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6655</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.0539</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.7194</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.4807</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.0907</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.8152</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.4439</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.3713</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.3917</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3917</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.3834</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.8883</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.4951</v>
-      </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4776</v>
+        <v>0.9705</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5266</v>
+        <v>-0.3025</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0042</v>
+        <v>1.273</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1868</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5676</v>
+        <v>-0.0747</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2513</v>
+        <v>-0.0272</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3163</v>
+        <v>-0.0474</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. KRATZER</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8072</v>
+        <v>-1.7675</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.135</v>
+        <v>-3.2426</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6722</v>
+        <v>1.4751</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8873</v>
+        <v>-2.4026</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1512</v>
+        <v>-0.917</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7361</v>
+        <v>-1.4856</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0168</v>
+        <v>-1.5841</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0168</v>
+        <v>-1.1022</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9041</v>
+        <v>-0.8185</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.168</v>
+        <v>0.1852</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7361</v>
+        <v>-1.0037</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="T10" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.6405</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>L. KRATZER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5156</v>
+        <v>-1.8072</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7891</v>
+        <v>-1.135</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2735</v>
+        <v>-0.6722</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4026</v>
+        <v>-0.8873</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.917</v>
+        <v>-0.1512</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4856</v>
+        <v>-0.7361</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5841</v>
+        <v>0.0168</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1022</v>
+        <v>0.0168</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.482</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8185</v>
+        <v>-0.9041</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1852</v>
+        <v>-0.168</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0037</v>
+        <v>-0.7361</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7187</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.187</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4683</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8201</v>
+        <v>-6.8805</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6161</v>
+        <v>-3.7773</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.204</v>
+        <v>-3.1032</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4572</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.315</v>
+        <v>0.2546</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1889</v>
+        <v>0.0277</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3584</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.6229</v>
+        <v>12.7432</v>
       </c>
       <c r="E13" t="n">
-        <v>5.314800000000002</v>
+        <v>6.4353</v>
       </c>
       <c r="F13" t="n">
-        <v>6.308199999999999</v>
+        <v>6.308099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6286</v>
+        <v>2.628599999999999</v>
       </c>
       <c r="H13" t="n">
         <v>8.133000000000003</v>
@@ -1441,7 +1441,7 @@
         <v>-5.5044</v>
       </c>
       <c r="J13" t="n">
-        <v>7.633400000000002</v>
+        <v>7.6334</v>
       </c>
       <c r="K13" t="n">
         <v>10.7296</v>
@@ -1468,13 +1468,13 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>2.319399999999999</v>
+        <v>3.4397</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0588</v>
+        <v>0.06160000000000003</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3784</v>
+        <v>3.3783</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2836000000000003</v>
@@ -1483,7 +1483,7 @@
         <v>6.858600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.142200000000001</v>
+        <v>-7.1422</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3108</v>
+        <v>4.0984</v>
       </c>
       <c r="E14" t="n">
         <v>2.266</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0448</v>
+        <v>1.8324</v>
       </c>
       <c r="G14" t="n">
         <v>0.7537</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2709</v>
+        <v>1.0585</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0861</v>
       </c>
       <c r="U14" t="n">
-        <v>1.357</v>
+        <v>1.1446</v>
       </c>
       <c r="V14" t="n">
         <v>2.2862</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2823</v>
+        <v>0.8116</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8611</v>
+        <v>0.2909</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4212</v>
+        <v>0.5208</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1269</v>
+        <v>-0.5105</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4646</v>
+        <v>0.0482</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6624</v>
+        <v>-0.5587</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4657</v>
+        <v>-0.0202</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8633999999999999</v>
+        <v>1.4788</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.4991</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6612</v>
+        <v>-0.4903</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6012</v>
+        <v>-1.4306</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.06</v>
+        <v>0.9403</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1773</v>
+        <v>0.2526</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2546</v>
+        <v>0.1693</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7387</v>
+        <v>0.5454</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4088</v>
+        <v>-0.4364</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3299</v>
+        <v>0.9818</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5105</v>
+        <v>-2.1269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0482</v>
+        <v>-1.4646</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5587</v>
+        <v>-0.6624</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0202</v>
+        <v>-1.4657</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4788</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4991</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4903</v>
+        <v>-0.6612</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4306</v>
+        <v>-0.6012</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9403</v>
+        <v>-0.06</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1797</v>
+        <v>0.4404</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2873</v>
+        <v>-0.0428</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1076</v>
+        <v>0.4832</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8438</v>
+        <v>-0.1263</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4128</v>
+        <v>-2.9031</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2566</v>
+        <v>2.7768</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3296</v>
+        <v>2.9766</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8453000000000001</v>
+        <v>0.3735</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1749</v>
+        <v>2.6031</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8443</v>
+        <v>0.9897</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7631</v>
+        <v>0.3511</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5147</v>
+        <v>1.9869</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9265</v>
+        <v>-0.2651</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4118</v>
+        <v>2.252</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2636</v>
+        <v>-0.232</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4857</v>
+        <v>-0.326</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2221</v>
+        <v>0.094</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1586</v>
+        <v>-0.7436</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3749</v>
+        <v>3.8452</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2163</v>
+        <v>-4.5888</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9766</v>
+        <v>0.8127</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3735</v>
+        <v>-0.3818</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6031</v>
+        <v>1.1945</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9897</v>
+        <v>4.1798</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6385999999999999</v>
+        <v>1.6672</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3511</v>
+        <v>2.5127</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9869</v>
+        <v>-3.3671</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2651</v>
+        <v>-2.0489</v>
       </c>
       <c r="O18" t="n">
-        <v>2.252</v>
+        <v>-1.3182</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.9432</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2643</v>
+        <v>-0.7007</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7978</v>
+        <v>-0.6956</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4665</v>
+        <v>-0.005</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.254</v>
+        <v>-0.944</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7272</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.9813</v>
+        <v>-1.5927</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8127</v>
+        <v>1.3296</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3818</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1945</v>
+        <v>2.1749</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1798</v>
+        <v>1.8443</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6672</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5127</v>
+        <v>1.7631</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3671</v>
+        <v>-0.5147</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0489</v>
+        <v>-0.9265</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3182</v>
+        <v>0.4118</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2112</v>
+        <v>-0.3637</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8136</v>
+        <v>-1.2498</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3976</v>
+        <v>0.8861</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6805</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7537</v>
+        <v>-1.4221</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9603</v>
+        <v>-1.5089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2067</v>
+        <v>0.0868</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5769</v>
+        <v>-1.1814</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.162</v>
+        <v>-1.7033</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4149</v>
+        <v>0.5219</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4455</v>
+        <v>-0.4948</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0168</v>
+        <v>-0.6519</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4623</v>
+        <v>0.1571</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8685</v>
+        <v>-0.6866</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1788</v>
+        <v>-1.0514</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0474</v>
+        <v>0.3648</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5685</v>
+        <v>-0.2407</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5149</v>
+        <v>0.1456</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0536</v>
+        <v>-0.3864</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8205</v>
+        <v>-1.6125</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3426</v>
+        <v>0.4606</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1631</v>
+        <v>-2.073</v>
       </c>
       <c r="G21" t="n">
         <v>0.5595</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046</v>
+        <v>0.3126</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0905</v>
+        <v>0.2084</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0141</v>
+        <v>0.1041</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3247</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1913</v>
+        <v>-1.6865</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8627</v>
+        <v>-1.9603</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3286</v>
+        <v>0.2739</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1814</v>
+        <v>-0.5769</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7033</v>
+        <v>-0.162</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5219</v>
+        <v>-0.4149</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4948</v>
+        <v>-1.4455</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6519</v>
+        <v>0.0168</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1571</v>
+        <v>-1.4623</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6866</v>
+        <v>0.8685</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0514</v>
+        <v>-0.1788</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3648</v>
+        <v>1.0474</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.01</v>
+        <v>-0.5012</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2082</v>
+        <v>-0.5149</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8017</v>
+        <v>0.0136</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8178</v>
+        <v>-3.7614</v>
       </c>
       <c r="E23" t="n">
         <v>-2.0859</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.732</v>
+        <v>-1.6755</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2763</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6137</v>
+        <v>-0.5573</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3229</v>
+        <v>-0.2664</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1149</v>
+        <v>-5.2094</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9706</v>
+        <v>-3.8527</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1443</v>
+        <v>-1.3567</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3885</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1208</v>
+        <v>-0.2153</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8136</v>
+        <v>-0.6956</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6928</v>
+        <v>0.4804</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6228</v>
+        <v>-10.0504</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2359</v>
+        <v>-5.235899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.387</v>
+        <v>-4.8142</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6284</v>
@@ -2377,13 +2377,13 @@
         <v>5.5044</v>
       </c>
       <c r="J25" t="n">
-        <v>5.004800000000001</v>
+        <v>5.0048</v>
       </c>
       <c r="K25" t="n">
         <v>2.5968</v>
       </c>
       <c r="L25" t="n">
-        <v>2.408</v>
+        <v>2.408000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-7.6334</v>
@@ -2404,22 +2404,22 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3196</v>
+        <v>-0.7468000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-3.3783</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0588</v>
+        <v>2.6315</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2836</v>
+        <v>0.2835999999999997</v>
       </c>
       <c r="W25" t="n">
         <v>8.214399999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.9308</v>
+        <v>-7.930800000000001</v>
       </c>
     </row>
   </sheetData>
